--- a/Result/profitability/6190.xlsx
+++ b/Result/profitability/6190.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>0.52125</v>
+        <v>0.56125</v>
       </c>
       <c r="N2" t="n">
-        <v>15.7725</v>
+        <v>15.59125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0.52125</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>15.295</v>
+        <v>15.18</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.12</v>
       </c>
       <c r="M4" t="n">
-        <v>0.44</v>
+        <v>0.465</v>
       </c>
       <c r="N4" t="n">
-        <v>14.22375</v>
+        <v>14.0775</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05624999999999997</v>
+        <v>0.1225</v>
       </c>
       <c r="N5" t="n">
-        <v>8.719999999999999</v>
+        <v>8.275</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06124999999999998</v>
+        <v>0.10875</v>
       </c>
       <c r="N6" t="n">
-        <v>7.55375</v>
+        <v>7.4275</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01499999999999998</v>
+        <v>0.05749999999999997</v>
       </c>
       <c r="N7" t="n">
-        <v>6.803750000000001</v>
+        <v>6.5825</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.65</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02374999999999998</v>
+        <v>0.08499999999999996</v>
       </c>
       <c r="N8" t="n">
-        <v>6.0125</v>
+        <v>6.02</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.12</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.01500000000000002</v>
+        <v>-0.01500000000000003</v>
       </c>
       <c r="N9" t="n">
         <v>5.795</v>
@@ -1772,7 +1772,7 @@
         <v>0.65</v>
       </c>
       <c r="M11" t="n">
-        <v>0.003749999999999989</v>
+        <v>0.003749999999999976</v>
       </c>
       <c r="N11" t="n">
         <v>5.16625</v>
@@ -1899,10 +1899,10 @@
         <v>0.49</v>
       </c>
       <c r="M12" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="N12" t="n">
-        <v>5.188750000000001</v>
+        <v>5.18875</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6190</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2979</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2524</v>
+      </c>
+      <c r="E75" t="n">
+        <v>455</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="G75" t="n">
+        <v>217</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>226</v>
+      </c>
+      <c r="K75" t="n">
+        <v>169</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.58875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.4975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.13953488372093</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.05999999999999872</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.003944773175542426</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.358974358974359</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.559999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1890600106213488</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
